--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97583</v>
+        <v>97588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99346</v>
+        <v>99351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97588</v>
+        <v>97590</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99351</v>
+        <v>99353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97590</v>
+        <v>97596</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97596</v>
+        <v>97598</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97598</v>
+        <v>97599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97599</v>
+        <v>97605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97605</v>
+        <v>97609</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97609</v>
+        <v>97611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97611</v>
+        <v>97613</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97613</v>
+        <v>97626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97626</v>
+        <v>97628</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97628</v>
+        <v>97631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97631</v>
+        <v>97641</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>

--- a/artfynd/A 33824-2026 artfynd.xlsx
+++ b/artfynd/A 33824-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136724541</v>
       </c>
       <c r="B2" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
         <v>136724609</v>
       </c>
       <c r="B3" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -945,7 +945,7 @@
         <v>136724749</v>
       </c>
       <c r="B4" t="n">
-        <v>97641</v>
+        <v>97642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1081,7 +1081,7 @@
         <v>136721495</v>
       </c>
       <c r="B5" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1197,7 +1197,7 @@
         <v>136721619</v>
       </c>
       <c r="B6" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1313,7 +1313,7 @@
         <v>136721691</v>
       </c>
       <c r="B7" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1429,7 +1429,7 @@
         <v>136721715</v>
       </c>
       <c r="B8" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
         <v>136721741</v>
       </c>
       <c r="B9" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1661,7 +1661,7 @@
         <v>136721829</v>
       </c>
       <c r="B10" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1777,7 +1777,7 @@
         <v>136721888</v>
       </c>
       <c r="B11" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1893,7 +1893,7 @@
         <v>136721990</v>
       </c>
       <c r="B12" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -2009,7 +2009,7 @@
         <v>136722021</v>
       </c>
       <c r="B13" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2125,7 +2125,7 @@
         <v>136722181</v>
       </c>
       <c r="B14" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2241,7 +2241,7 @@
         <v>136722588</v>
       </c>
       <c r="B15" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>136722642</v>
       </c>
       <c r="B16" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2473,7 +2473,7 @@
         <v>136722741</v>
       </c>
       <c r="B17" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2589,7 +2589,7 @@
         <v>136722807</v>
       </c>
       <c r="B18" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>136722847</v>
       </c>
       <c r="B19" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>136722919</v>
       </c>
       <c r="B20" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2937,7 +2937,7 @@
         <v>136723071</v>
       </c>
       <c r="B21" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3053,7 +3053,7 @@
         <v>136723156</v>
       </c>
       <c r="B22" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3164,7 +3164,7 @@
         <v>136723244</v>
       </c>
       <c r="B23" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3280,7 +3280,7 @@
         <v>136723297</v>
       </c>
       <c r="B24" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3396,7 +3396,7 @@
         <v>136723347</v>
       </c>
       <c r="B25" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3512,7 +3512,7 @@
         <v>136723444</v>
       </c>
       <c r="B26" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
         <v>136723516</v>
       </c>
       <c r="B27" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3744,7 +3744,7 @@
         <v>136723625</v>
       </c>
       <c r="B28" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>136723706</v>
       </c>
       <c r="B29" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3976,7 +3976,7 @@
         <v>136723914</v>
       </c>
       <c r="B30" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
         <v>136723966</v>
       </c>
       <c r="B31" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4208,7 +4208,7 @@
         <v>136724047</v>
       </c>
       <c r="B32" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4324,7 +4324,7 @@
         <v>136724099</v>
       </c>
       <c r="B33" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4435,7 +4435,7 @@
         <v>136724159</v>
       </c>
       <c r="B34" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4551,7 +4551,7 @@
         <v>136724256</v>
       </c>
       <c r="B35" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4667,7 +4667,7 @@
         <v>136724374</v>
       </c>
       <c r="B36" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
